--- a/resources/M673/M673_codebaseline.xlsx
+++ b/resources/M673/M673_codebaseline.xlsx
@@ -543,7 +543,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>0.002384777448566076</v>
+        <v>0.002341179102930021</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -551,7 +551,7 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>8.894274866446905E-05</v>
+        <v>8.73167031395812E-05</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -567,7 +567,7 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>0.0009227810173938663</v>
+        <v>0.0009495691466429457</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -575,7 +575,7 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>0.001567615945211267</v>
+        <v>0.001686303829383162</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -583,7 +583,7 @@
         <v>7</v>
       </c>
       <c r="B7">
-        <v>5.558921791529315E-06</v>
+        <v>5.457293946223825E-06</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -591,7 +591,7 @@
         <v>8</v>
       </c>
       <c r="B8">
-        <v>0.0001778854973289381</v>
+        <v>0.0001746334062791624</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -599,7 +599,7 @@
         <v>9</v>
       </c>
       <c r="B9">
-        <v>1.111784358305863E-05</v>
+        <v>1.091458789244765E-05</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -607,7 +607,7 @@
         <v>10</v>
       </c>
       <c r="B10">
-        <v>0.000105619514039057</v>
+        <v>0.0001036885849782527</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -615,7 +615,7 @@
         <v>11</v>
       </c>
       <c r="B11">
-        <v>2.223568716611726E-05</v>
+        <v>2.18291757848953E-05</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -623,7 +623,7 @@
         <v>12</v>
       </c>
       <c r="B12">
-        <v>0.0002501514806188192</v>
+        <v>0.0002455782275800721</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -631,7 +631,7 @@
         <v>13</v>
       </c>
       <c r="B13">
-        <v>1.667676537458794E-05</v>
+        <v>1.637188183867148E-05</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -639,7 +639,7 @@
         <v>14</v>
       </c>
       <c r="B14">
-        <v>0.0001778854973289381</v>
+        <v>0.0001746334062791624</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -655,7 +655,7 @@
         <v>16</v>
       </c>
       <c r="B16">
-        <v>1.667676537458794E-05</v>
+        <v>1.637188183867148E-05</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -663,7 +663,7 @@
         <v>17</v>
       </c>
       <c r="B17">
-        <v>9.450167045599836E-05</v>
+        <v>9.277399708580504E-05</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -671,7 +671,7 @@
         <v>18</v>
       </c>
       <c r="B18">
-        <v>3.335353074917589E-05</v>
+        <v>3.274376367734296E-05</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -687,7 +687,7 @@
         <v>20</v>
       </c>
       <c r="B20">
-        <v>0.01058974601286334</v>
+        <v>0.01071812531038359</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -695,7 +695,7 @@
         <v>21</v>
       </c>
       <c r="B21">
-        <v>0.003174144342963239</v>
+        <v>0.003383522246658772</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -703,7 +703,7 @@
         <v>22</v>
       </c>
       <c r="B22">
-        <v>0.0002279157934527019</v>
+        <v>0.0002237490517951768</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -711,7 +711,7 @@
         <v>23</v>
       </c>
       <c r="B23">
-        <v>1.111784358305863E-05</v>
+        <v>1.091458789244765E-05</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -719,7 +719,7 @@
         <v>24</v>
       </c>
       <c r="B24">
-        <v>3.89124525407052E-05</v>
+        <v>3.820105762356678E-05</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -727,7 +727,7 @@
         <v>25</v>
       </c>
       <c r="B25">
-        <v>0.0006893063021496351</v>
+        <v>0.0006767044493317544</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -735,7 +735,7 @@
         <v>26</v>
       </c>
       <c r="B26">
-        <v>0.0001389730447882329</v>
+        <v>0.0001364323486555956</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -743,7 +743,7 @@
         <v>27</v>
       </c>
       <c r="B27">
-        <v>0.0005058618830291676</v>
+        <v>0.0004966137491063681</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -751,7 +751,7 @@
         <v>28</v>
       </c>
       <c r="B28">
-        <v>0.001417525056839975</v>
+        <v>0.001391609956287075</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -759,7 +759,7 @@
         <v>29</v>
       </c>
       <c r="B29">
-        <v>3.89124525407052E-05</v>
+        <v>3.820105762356678E-05</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -767,7 +767,7 @@
         <v>30</v>
       </c>
       <c r="B30">
-        <v>1.667676537458794E-05</v>
+        <v>1.637188183867148E-05</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -791,7 +791,7 @@
         <v>33</v>
       </c>
       <c r="B33">
-        <v>5.558921791529315E-06</v>
+        <v>5.457293946223825E-06</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -799,7 +799,7 @@
         <v>34</v>
       </c>
       <c r="B34">
-        <v>5.558921791529315E-06</v>
+        <v>5.457293946223825E-06</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -807,7 +807,7 @@
         <v>35</v>
       </c>
       <c r="B35">
-        <v>1.667676537458794E-05</v>
+        <v>1.637188183867148E-05</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -815,7 +815,7 @@
         <v>36</v>
       </c>
       <c r="B36">
-        <v>0.002896198253386773</v>
+        <v>0.002843250145982613</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -823,7 +823,7 @@
         <v>37</v>
       </c>
       <c r="B37">
-        <v>0.0006615116931919884</v>
+        <v>0.0006494179796006352</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -831,7 +831,7 @@
         <v>38</v>
       </c>
       <c r="B38">
-        <v>0.004402666058891218</v>
+        <v>0.00432217680540927</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -839,7 +839,7 @@
         <v>39</v>
       </c>
       <c r="B39">
-        <v>0.000300181776742583</v>
+        <v>0.0002946938730960866</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -847,7 +847,7 @@
         <v>40</v>
       </c>
       <c r="B40">
-        <v>2.223568716611726E-05</v>
+        <v>2.18291757848953E-05</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -855,7 +855,7 @@
         <v>41</v>
       </c>
       <c r="B41">
-        <v>5.558921791529315E-06</v>
+        <v>5.457293946223825E-06</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -863,7 +863,7 @@
         <v>42</v>
       </c>
       <c r="B42">
-        <v>0.003802302505406051</v>
+        <v>0.003732789059217097</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -871,7 +871,7 @@
         <v>43</v>
       </c>
       <c r="B43">
-        <v>1.667676537458794E-05</v>
+        <v>1.637188183867148E-05</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -879,7 +879,7 @@
         <v>44</v>
       </c>
       <c r="B44">
-        <v>5.558921791529315E-06</v>
+        <v>5.457293946223825E-06</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -887,7 +887,7 @@
         <v>45</v>
       </c>
       <c r="B45">
-        <v>5.558921791529315E-05</v>
+        <v>5.457293946223825E-05</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -895,7 +895,7 @@
         <v>46</v>
       </c>
       <c r="B46">
-        <v>5.558921791529315E-06</v>
+        <v>5.457293946223825E-06</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -903,7 +903,7 @@
         <v>47</v>
       </c>
       <c r="B47">
-        <v>5.558921791529315E-06</v>
+        <v>5.457293946223825E-06</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -911,7 +911,7 @@
         <v>48</v>
       </c>
       <c r="B48">
-        <v>5.558921791529315E-06</v>
+        <v>5.457293946223825E-06</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -919,7 +919,7 @@
         <v>49</v>
       </c>
       <c r="B49">
-        <v>0.001584292710585855</v>
+        <v>0.00155532877467379</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -927,7 +927,7 @@
         <v>50</v>
       </c>
       <c r="B50">
-        <v>0.003602181320910996</v>
+        <v>0.003536326477153039</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -935,7 +935,7 @@
         <v>51</v>
       </c>
       <c r="B51">
-        <v>0.003846773879738286</v>
+        <v>0.003776447410786887</v>
       </c>
     </row>
   </sheetData>

--- a/resources/M673/M673_codebaseline.xlsx
+++ b/resources/M673/M673_codebaseline.xlsx
@@ -543,7 +543,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>0.002341179102930021</v>
+        <v>0.002338728582098096</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -551,7 +551,7 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>8.73167031395812E-05</v>
+        <v>8.722530842323901E-05</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -559,7 +559,7 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>0.0001055069051492923</v>
+        <v>0.0001035800537525963</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -567,7 +567,7 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>0.0009495691466429457</v>
+        <v>0.0009485752291027242</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -575,7 +575,7 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>0.001686303829383162</v>
+        <v>0.001684538768923803</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -583,7 +583,7 @@
         <v>7</v>
       </c>
       <c r="B7">
-        <v>5.457293946223825E-06</v>
+        <v>5.451581776452438E-06</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -591,7 +591,7 @@
         <v>8</v>
       </c>
       <c r="B8">
-        <v>0.0001746334062791624</v>
+        <v>0.000174450616846478</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -599,7 +599,7 @@
         <v>9</v>
       </c>
       <c r="B9">
-        <v>1.091458789244765E-05</v>
+        <v>1.090316355290488E-05</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -607,7 +607,7 @@
         <v>10</v>
       </c>
       <c r="B10">
-        <v>0.0001036885849782527</v>
+        <v>0.0001035800537525963</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -615,7 +615,7 @@
         <v>11</v>
       </c>
       <c r="B11">
-        <v>2.18291757848953E-05</v>
+        <v>2.180632710580975E-05</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -623,7 +623,7 @@
         <v>12</v>
       </c>
       <c r="B12">
-        <v>0.0002455782275800721</v>
+        <v>0.0002453211799403597</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -631,7 +631,7 @@
         <v>13</v>
       </c>
       <c r="B13">
-        <v>1.637188183867148E-05</v>
+        <v>1.635474532935731E-05</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -639,7 +639,7 @@
         <v>14</v>
       </c>
       <c r="B14">
-        <v>0.0001746334062791624</v>
+        <v>0.000174450616846478</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -655,7 +655,7 @@
         <v>16</v>
       </c>
       <c r="B16">
-        <v>1.637188183867148E-05</v>
+        <v>1.635474532935731E-05</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -663,7 +663,7 @@
         <v>17</v>
       </c>
       <c r="B17">
-        <v>9.277399708580504E-05</v>
+        <v>9.267689019969145E-05</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -671,7 +671,7 @@
         <v>18</v>
       </c>
       <c r="B18">
-        <v>3.274376367734296E-05</v>
+        <v>3.270949065871463E-05</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -679,7 +679,7 @@
         <v>19</v>
       </c>
       <c r="B19">
-        <v>4.44239600628599E-05</v>
+        <v>4.36126542116195E-05</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -687,7 +687,7 @@
         <v>20</v>
       </c>
       <c r="B20">
-        <v>0.01071812531038359</v>
+        <v>0.01070690660895259</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -695,7 +695,7 @@
         <v>21</v>
       </c>
       <c r="B21">
-        <v>0.003383522246658772</v>
+        <v>0.003379980701400511</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -703,7 +703,7 @@
         <v>22</v>
       </c>
       <c r="B22">
-        <v>0.0002237490517951768</v>
+        <v>0.00022351485283455</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -711,7 +711,7 @@
         <v>23</v>
       </c>
       <c r="B23">
-        <v>1.091458789244765E-05</v>
+        <v>1.090316355290488E-05</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -719,7 +719,7 @@
         <v>24</v>
       </c>
       <c r="B24">
-        <v>3.820105762356678E-05</v>
+        <v>3.816107243516707E-05</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -727,7 +727,7 @@
         <v>25</v>
       </c>
       <c r="B25">
-        <v>0.0006767044493317544</v>
+        <v>0.0006759961402801023</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -735,7 +735,7 @@
         <v>26</v>
       </c>
       <c r="B26">
-        <v>0.0001364323486555956</v>
+        <v>0.0001362895444113109</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -743,7 +743,7 @@
         <v>27</v>
       </c>
       <c r="B27">
-        <v>0.0004966137491063681</v>
+        <v>0.0004960939416571718</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -751,7 +751,7 @@
         <v>28</v>
       </c>
       <c r="B28">
-        <v>0.001391609956287075</v>
+        <v>0.001390153352995372</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -759,7 +759,7 @@
         <v>29</v>
       </c>
       <c r="B29">
-        <v>3.820105762356678E-05</v>
+        <v>3.816107243516707E-05</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -767,7 +767,7 @@
         <v>30</v>
       </c>
       <c r="B30">
-        <v>1.637188183867148E-05</v>
+        <v>1.635474532935731E-05</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -775,7 +775,7 @@
         <v>31</v>
       </c>
       <c r="B31">
-        <v>0.000910691181288628</v>
+        <v>0.0008940594113381998</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -783,7 +783,7 @@
         <v>32</v>
       </c>
       <c r="B32">
-        <v>1.110599001571498E-05</v>
+        <v>1.090316355290488E-05</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -791,7 +791,7 @@
         <v>33</v>
       </c>
       <c r="B33">
-        <v>5.457293946223825E-06</v>
+        <v>5.451581776452438E-06</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -799,7 +799,7 @@
         <v>34</v>
       </c>
       <c r="B34">
-        <v>5.457293946223825E-06</v>
+        <v>5.451581776452438E-06</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -807,7 +807,7 @@
         <v>35</v>
       </c>
       <c r="B35">
-        <v>1.637188183867148E-05</v>
+        <v>1.635474532935731E-05</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -815,7 +815,7 @@
         <v>36</v>
       </c>
       <c r="B36">
-        <v>0.002843250145982613</v>
+        <v>0.00284027410553172</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -823,7 +823,7 @@
         <v>37</v>
       </c>
       <c r="B37">
-        <v>0.0006494179796006352</v>
+        <v>0.0006487382313978401</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -831,7 +831,7 @@
         <v>38</v>
       </c>
       <c r="B38">
-        <v>0.00432217680540927</v>
+        <v>0.00431765276695033</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -839,7 +839,7 @@
         <v>39</v>
       </c>
       <c r="B39">
-        <v>0.0002946938730960866</v>
+        <v>0.0002943854159284317</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -847,7 +847,7 @@
         <v>40</v>
       </c>
       <c r="B40">
-        <v>2.18291757848953E-05</v>
+        <v>2.180632710580975E-05</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -855,7 +855,7 @@
         <v>41</v>
       </c>
       <c r="B41">
-        <v>5.457293946223825E-06</v>
+        <v>5.451581776452438E-06</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -863,7 +863,7 @@
         <v>42</v>
       </c>
       <c r="B42">
-        <v>0.003732789059217097</v>
+        <v>0.003728881935093467</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -871,7 +871,7 @@
         <v>43</v>
       </c>
       <c r="B43">
-        <v>1.637188183867148E-05</v>
+        <v>1.635474532935731E-05</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -879,7 +879,7 @@
         <v>44</v>
       </c>
       <c r="B44">
-        <v>5.457293946223825E-06</v>
+        <v>5.451581776452438E-06</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -887,7 +887,7 @@
         <v>45</v>
       </c>
       <c r="B45">
-        <v>5.457293946223825E-05</v>
+        <v>5.451581776452438E-05</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -895,7 +895,7 @@
         <v>46</v>
       </c>
       <c r="B46">
-        <v>5.457293946223825E-06</v>
+        <v>5.451581776452438E-06</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -903,7 +903,7 @@
         <v>47</v>
       </c>
       <c r="B47">
-        <v>5.457293946223825E-06</v>
+        <v>5.451581776452438E-06</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -911,7 +911,7 @@
         <v>48</v>
       </c>
       <c r="B48">
-        <v>5.457293946223825E-06</v>
+        <v>5.451581776452438E-06</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -919,7 +919,7 @@
         <v>49</v>
       </c>
       <c r="B49">
-        <v>0.00155532877467379</v>
+        <v>0.001553700806288945</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -927,7 +927,7 @@
         <v>50</v>
       </c>
       <c r="B50">
-        <v>0.003536326477153039</v>
+        <v>0.00353262499114118</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -935,7 +935,7 @@
         <v>51</v>
       </c>
       <c r="B51">
-        <v>0.003776447410786887</v>
+        <v>0.003772494589305087</v>
       </c>
     </row>
   </sheetData>

--- a/resources/M673/M673_codebaseline.xlsx
+++ b/resources/M673/M673_codebaseline.xlsx
@@ -543,7 +543,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>0.002338728582098096</v>
+        <v>0.003043434153128216</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -551,7 +551,7 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>8.722530842323901E-05</v>
+        <v>5.797017434529934E-05</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -559,7 +559,7 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>0.0001035800537525963</v>
+        <v>8.33215596346893E-05</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -567,7 +567,7 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>0.0009485752291027242</v>
+        <v>0.0008405675280068405</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -575,7 +575,7 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>0.001684538768923803</v>
+        <v>0.001402153591976928</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -583,7 +583,7 @@
         <v>7</v>
       </c>
       <c r="B7">
-        <v>5.451581776452438E-06</v>
+        <v>7.246271793162418E-06</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -591,7 +591,7 @@
         <v>8</v>
       </c>
       <c r="B8">
-        <v>0.000174450616846478</v>
+        <v>0.0001594179794495732</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -599,7 +599,7 @@
         <v>9</v>
       </c>
       <c r="B9">
-        <v>1.090316355290488E-05</v>
+        <v>7.246271793162418E-06</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -607,7 +607,7 @@
         <v>10</v>
       </c>
       <c r="B10">
-        <v>0.0001035800537525963</v>
+        <v>7.97089897247866E-05</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -615,7 +615,7 @@
         <v>11</v>
       </c>
       <c r="B11">
-        <v>2.180632710580975E-05</v>
+        <v>1.449254358632484E-05</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -623,7 +623,7 @@
         <v>12</v>
       </c>
       <c r="B12">
-        <v>0.0002453211799403597</v>
+        <v>0.0002210112896914538</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -631,7 +631,7 @@
         <v>13</v>
       </c>
       <c r="B13">
-        <v>1.635474532935731E-05</v>
+        <v>1.086940768974363E-05</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -639,7 +639,7 @@
         <v>14</v>
       </c>
       <c r="B14">
-        <v>0.000174450616846478</v>
+        <v>0.0001304328922769235</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -655,7 +655,7 @@
         <v>16</v>
       </c>
       <c r="B16">
-        <v>1.635474532935731E-05</v>
+        <v>1.086940768974363E-05</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -663,7 +663,7 @@
         <v>17</v>
       </c>
       <c r="B17">
-        <v>9.267689019969145E-05</v>
+        <v>6.159331024188056E-05</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -671,7 +671,7 @@
         <v>18</v>
       </c>
       <c r="B18">
-        <v>3.270949065871463E-05</v>
+        <v>2.536195127606846E-05</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -679,7 +679,7 @@
         <v>19</v>
       </c>
       <c r="B19">
-        <v>4.36126542116195E-05</v>
+        <v>4.709479457612874E-05</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -687,7 +687,7 @@
         <v>20</v>
       </c>
       <c r="B20">
-        <v>0.01070690660895259</v>
+        <v>0.01117737424095303</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -695,7 +695,7 @@
         <v>21</v>
       </c>
       <c r="B21">
-        <v>0.003379980701400511</v>
+        <v>0.003344154432544456</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -703,7 +703,7 @@
         <v>22</v>
       </c>
       <c r="B22">
-        <v>0.00022351485283455</v>
+        <v>0.000173910523035898</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -711,7 +711,7 @@
         <v>23</v>
       </c>
       <c r="B23">
-        <v>1.090316355290488E-05</v>
+        <v>7.246271793162418E-06</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -719,7 +719,7 @@
         <v>24</v>
       </c>
       <c r="B24">
-        <v>3.816107243516707E-05</v>
+        <v>3.623135896581209E-05</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -727,7 +727,7 @@
         <v>25</v>
       </c>
       <c r="B25">
-        <v>0.0006759961402801023</v>
+        <v>0.000467384530658976</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -735,7 +735,7 @@
         <v>26</v>
       </c>
       <c r="B26">
-        <v>0.0001362895444113109</v>
+        <v>9.420153331111143E-05</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -743,7 +743,7 @@
         <v>27</v>
       </c>
       <c r="B27">
-        <v>0.0004960939416571718</v>
+        <v>0.0003659367255547021</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -751,7 +751,7 @@
         <v>28</v>
       </c>
       <c r="B28">
-        <v>0.001390153352995372</v>
+        <v>0.0009311459254213707</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -759,7 +759,7 @@
         <v>29</v>
       </c>
       <c r="B29">
-        <v>3.816107243516707E-05</v>
+        <v>2.898508717264967E-05</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -767,7 +767,7 @@
         <v>30</v>
       </c>
       <c r="B30">
-        <v>1.635474532935731E-05</v>
+        <v>1.086940768974363E-05</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -775,7 +775,7 @@
         <v>31</v>
       </c>
       <c r="B31">
-        <v>0.0008940594113381998</v>
+        <v>0.0007101346357299169</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -783,7 +783,7 @@
         <v>32</v>
       </c>
       <c r="B32">
-        <v>1.090316355290488E-05</v>
+        <v>7.246271793162418E-06</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -791,7 +791,7 @@
         <v>33</v>
       </c>
       <c r="B33">
-        <v>5.451581776452438E-06</v>
+        <v>3.623135896581209E-06</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -799,7 +799,7 @@
         <v>34</v>
       </c>
       <c r="B34">
-        <v>5.451581776452438E-06</v>
+        <v>1.449254358632484E-05</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -807,7 +807,7 @@
         <v>35</v>
       </c>
       <c r="B35">
-        <v>1.635474532935731E-05</v>
+        <v>1.086940768974363E-05</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -815,7 +815,7 @@
         <v>36</v>
       </c>
       <c r="B36">
-        <v>0.00284027410553172</v>
+        <v>0.002184750945638469</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -823,7 +823,7 @@
         <v>37</v>
       </c>
       <c r="B37">
-        <v>0.0006487382313978401</v>
+        <v>0.0005398472485906001</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -831,7 +831,7 @@
         <v>38</v>
       </c>
       <c r="B38">
-        <v>0.00431765276695033</v>
+        <v>0.003518064955580354</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -839,7 +839,7 @@
         <v>39</v>
       </c>
       <c r="B39">
-        <v>0.0002943854159284317</v>
+        <v>0.0001956493384153853</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -847,7 +847,7 @@
         <v>40</v>
       </c>
       <c r="B40">
-        <v>2.180632710580975E-05</v>
+        <v>1.449254358632484E-05</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -855,7 +855,7 @@
         <v>41</v>
       </c>
       <c r="B41">
-        <v>5.451581776452438E-06</v>
+        <v>3.623135896581209E-06</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -863,7 +863,7 @@
         <v>42</v>
       </c>
       <c r="B42">
-        <v>0.003728881935093467</v>
+        <v>0.003061549832611122</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -871,7 +871,7 @@
         <v>43</v>
       </c>
       <c r="B43">
-        <v>1.635474532935731E-05</v>
+        <v>2.173881537948725E-05</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -879,7 +879,7 @@
         <v>44</v>
       </c>
       <c r="B44">
-        <v>5.451581776452438E-06</v>
+        <v>3.623135896581209E-06</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -887,7 +887,7 @@
         <v>45</v>
       </c>
       <c r="B45">
-        <v>5.451581776452438E-05</v>
+        <v>3.623135896581209E-05</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -895,7 +895,7 @@
         <v>46</v>
       </c>
       <c r="B46">
-        <v>5.451581776452438E-06</v>
+        <v>1.449254358632484E-05</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -903,7 +903,7 @@
         <v>47</v>
       </c>
       <c r="B47">
-        <v>5.451581776452438E-06</v>
+        <v>3.623135896581209E-06</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -911,7 +911,7 @@
         <v>48</v>
       </c>
       <c r="B48">
-        <v>5.451581776452438E-06</v>
+        <v>3.623135896581209E-06</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -919,7 +919,7 @@
         <v>49</v>
       </c>
       <c r="B49">
-        <v>0.001553700806288945</v>
+        <v>0.001173896030492312</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -927,7 +927,7 @@
         <v>50</v>
       </c>
       <c r="B50">
-        <v>0.00353262499114118</v>
+        <v>0.002818799727540181</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -935,7 +935,7 @@
         <v>51</v>
       </c>
       <c r="B51">
-        <v>0.003772494589305087</v>
+        <v>0.002717351922435907</v>
       </c>
     </row>
   </sheetData>

--- a/resources/M673/M673_codebaseline.xlsx
+++ b/resources/M673/M673_codebaseline.xlsx
@@ -448,7 +448,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.00316</v>
+        <v>0.00317</v>
       </c>
     </row>
     <row r="3">
@@ -478,7 +478,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.00143</v>
+        <v>0.00144</v>
       </c>
     </row>
     <row r="6">
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.01206</v>
+        <v>0.008460000000000001</v>
       </c>
     </row>
     <row r="18">
@@ -608,7 +608,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.00362</v>
+        <v>0.00363</v>
       </c>
     </row>
     <row r="19">
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.00148</v>
+        <v>0.00149</v>
       </c>
     </row>
     <row r="26">
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.00038</v>
+        <v>0.00076</v>
       </c>
     </row>
     <row r="29">
@@ -718,7 +718,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>1e-05</v>
       </c>
     </row>
     <row r="30">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.00229</v>
+        <v>0.0023</v>
       </c>
     </row>
     <row r="34">
@@ -768,7 +768,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.00054</v>
+        <v>0.00055</v>
       </c>
     </row>
     <row r="35">
@@ -778,7 +778,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.00377</v>
+        <v>0.00302</v>
       </c>
     </row>
     <row r="36">
@@ -828,7 +828,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.00447</v>
+        <v>0.00449</v>
       </c>
     </row>
     <row r="41">
@@ -908,7 +908,7 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.00327</v>
+        <v>0.00328</v>
       </c>
     </row>
     <row r="49">
@@ -918,7 +918,7 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.00405</v>
+        <v>0.00541</v>
       </c>
     </row>
   </sheetData>
@@ -967,7 +967,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-18T09:30:31.520752</t>
+          <t>2026-06-18T09:51:49.490807</t>
         </is>
       </c>
     </row>
@@ -1039,7 +1039,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>G向ELA Mura=0;S向ELA Mura=0;大面积亮点=0.5;大面积暗点=0.5;暗点=1.5;群暗点=1.5</t>
+          <t>G向ELA Mura=0;S向ELA Mura=0;S向亮线=0.7;彩斑Mura=0.8;暗点=1.5;群暗点=2</t>
         </is>
       </c>
     </row>

--- a/resources/M673/M673_codebaseline.xlsx
+++ b/resources/M673/M673_codebaseline.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B49"/>
+  <dimension ref="A1:B55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,7 +448,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.00317</v>
+        <v>0.00456</v>
       </c>
     </row>
     <row r="3">
@@ -458,7 +458,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5e-05</v>
+        <v>6e-05</v>
       </c>
     </row>
     <row r="4">
@@ -468,7 +468,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.00085</v>
+        <v>0.00092</v>
       </c>
     </row>
     <row r="5">
@@ -478,7 +478,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.00144</v>
+        <v>0.00143</v>
       </c>
     </row>
     <row r="6">
@@ -488,7 +488,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1e-05</v>
+        <v>2e-05</v>
       </c>
     </row>
     <row r="7">
@@ -498,7 +498,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.00015</v>
+        <v>0.00019</v>
       </c>
     </row>
     <row r="8">
@@ -518,7 +518,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6.999999999999999e-05</v>
+        <v>0.00011</v>
       </c>
     </row>
     <row r="10">
@@ -528,7 +528,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2e-05</v>
+        <v>3e-05</v>
       </c>
     </row>
     <row r="11">
@@ -538,7 +538,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.00024</v>
+        <v>0.00027</v>
       </c>
     </row>
     <row r="12">
@@ -554,187 +554,187 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>L3亮点</t>
+          <t>IC侧 Mura</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.00012</v>
+        <v>1e-05</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>PCD裂纹亮线</t>
+          <t>IC侧长条形Mura</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1e-05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>RGB亮点</t>
+          <t>L3亮点</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6e-05</v>
+        <v>0.00041</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>RGB黑斑</t>
+          <t>PCD裂纹亮线</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2e-05</v>
+        <v>1e-05</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S向亮线</t>
+          <t>RGB亮点</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.008460000000000001</v>
+        <v>0.00013</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S向单暗线</t>
+          <t>RGB黑斑</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.00363</v>
+        <v>0.0001</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S向带状Mura</t>
+          <t>S向亮线</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.00017</v>
+        <v>0.00728</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S向彩色带状Mura</t>
+          <t>S向单暗线</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1e-05</v>
+        <v>0.0033</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S向微亮线</t>
+          <t>S向带状Mura</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3e-05</v>
+        <v>0.00016</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>S向棱形彩色带状Mura</t>
+          <t>S向彩色带状Mura</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.00043</v>
+        <v>1e-05</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>S向群亮线</t>
+          <t>S向微亮线</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.0001</v>
+        <v>3e-05</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>S向边缘Mura</t>
+          <t>S向棱形彩色带状Mura</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.00035</v>
+        <v>0.00044</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>单亮点</t>
+          <t>S向群亮线</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.00149</v>
+        <v>9.000000000000001e-05</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>可修复暗点</t>
+          <t>S向群暗线</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3e-05</v>
+        <v>1e-05</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>大圆环Mura</t>
+          <t>S向边缘Mura</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1e-05</v>
+        <v>0.00037</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>大面积亮点</t>
+          <t>单亮点</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.00076</v>
+        <v>0.00163</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>大面积暗点</t>
+          <t>可修复亮点</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1e-05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>大面积片状彩斑Mura</t>
+          <t>可修复暗点</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>3e-05</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>孔区跑道Mura</t>
+          <t>大圆环Mura</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -744,57 +744,57 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>左斜黑色带状Mura</t>
+          <t>大面积亮点</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1e-05</v>
+        <v>0.00092</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>常亮白斑</t>
+          <t>大面积暗点</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.0023</v>
+        <v>1e-05</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>常暗黑斑Mura</t>
+          <t>大面积片状彩斑Mura</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.00055</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>彩斑Mura</t>
+          <t>孔区环状Mura</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.00302</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>微亮点</t>
+          <t>孔区跑道Mura</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.00018</v>
+        <v>1e-05</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>微暗点</t>
+          <t>左斜黑色带状Mura</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -804,67 +804,67 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>摩尔纹</t>
+          <t>常亮白斑</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0</v>
+        <v>0.00444</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>斑中带点</t>
+          <t>常暗黑斑Mura</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1e-05</v>
+        <v>0.0007</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>暗点</t>
+          <t>彩斑Mura</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.00449</v>
+        <v>0.00537</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>流星状划线</t>
+          <t>微亮点</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>2e-05</v>
+        <v>0.00017</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>灰阶块状白斑Mura</t>
+          <t>微暗点</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0</v>
+        <v>1e-05</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>灰阶小白斑Mura</t>
+          <t>摩尔纹</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>3e-05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>灰阶暗点</t>
+          <t>斑中带点</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -874,51 +874,111 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>灰阶点状白斑Mura</t>
+          <t>暗点</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0</v>
+        <v>0.00779</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>环状Mura</t>
+          <t>流星状划线</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0</v>
+        <v>3e-05</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>白画面黑斑Mura</t>
+          <t>灰阶块状白斑Mura</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.00119</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>群亮点</t>
+          <t>灰阶小白斑Mura</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.00328</v>
+        <v>8.000000000000001e-05</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
+          <t>灰阶暗点</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>2e-05</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>灰阶点状白斑Mura</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>1e-05</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>环状Mura</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>2e-05</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>白画面黑斑Mura</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>0.00187</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>群亮点</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>0.00647</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
           <t>群暗点</t>
         </is>
       </c>
-      <c r="B49" t="n">
-        <v>0.00541</v>
+      <c r="B54" t="n">
+        <v>0.00458</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>雪花状Mura</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -967,7 +1027,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-18T09:51:49.490807</t>
+          <t>2026-06-30T11:38:51.331457</t>
         </is>
       </c>
     </row>
@@ -1015,7 +1075,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-30</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1087,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>54</t>
         </is>
       </c>
     </row>
@@ -1039,7 +1099,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>G向ELA Mura=0;S向ELA Mura=0;S向亮线=0.7;彩斑Mura=0.8;暗点=1.5;群暗点=2</t>
+          <t>G向ELA Mura=0;S向ELA Mura=0;S向亮线=0.7;暗点=1.8;群亮点=1.2;群暗点=1.2</t>
         </is>
       </c>
     </row>
